--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99266</v>
+        <v>99271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99271</v>
+        <v>99273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14850-2025 artfynd.xlsx
+++ b/artfynd/A 14850-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438213</v>
       </c>
       <c r="B2" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
